--- a/estadistica2/data/velasquez_faure.xlsx
+++ b/estadistica2/data/velasquez_faure.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10329"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kennethbunker/Library/CloudStorage/Dropbox/GitHub/uss/estadistica2/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41300B40-7A70-8147-972B-6ADABDC002C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B78D78C6-8C74-EB4B-B732-38ECA218ADF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,7 @@
     <sheet name="codebook" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">codebook!$A$1:$E$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="33">
   <si>
     <t>country_name</t>
   </si>
@@ -119,6 +120,21 @@
   </si>
   <si>
     <t>ethnic</t>
+  </si>
+  <si>
+    <t>variable</t>
+  </si>
+  <si>
+    <t>descripcion</t>
+  </si>
+  <si>
+    <t>medicion</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>max</t>
   </si>
 </sst>
 </file>
@@ -632,7 +648,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
@@ -641,6 +657,8 @@
     <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1000,6 +1018,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="10.83203125" customWidth="1"/>
     <col min="6" max="6" width="11.5" style="4"/>
     <col min="7" max="7" width="11.5" style="2"/>
@@ -6799,9 +6818,86 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1BBE8D6-39CA-7F44-81E8-2B0BB2DB2329}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="8" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:E1" xr:uid="{D1BBE8D6-39CA-7F44-81E8-2B0BB2DB2329}"/>
+  <conditionalFormatting sqref="A2">
+    <cfRule type="duplicateValues" priority="1"/>
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/estadistica2/data/velasquez_faure.xlsx
+++ b/estadistica2/data/velasquez_faure.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kennethbunker/Library/CloudStorage/Dropbox/GitHub/uss/estadistica2/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B78D78C6-8C74-EB4B-B732-38ECA218ADF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A342D77D-C8CB-D443-863E-D96338427EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,11 +17,13 @@
     <sheet name="codebook" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">codebook!$A$1:$E$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$I$1</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -29,6 +31,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="38">
   <si>
     <t>country_name</t>
   </si>
@@ -53,13 +57,16 @@
     <t>time</t>
   </si>
   <si>
+    <t>enpv_bn</t>
+  </si>
+  <si>
     <t>dep_as</t>
   </si>
   <si>
     <t>dep_dm</t>
   </si>
   <si>
-    <t>enpv_bn</t>
+    <t>ethnic</t>
   </si>
   <si>
     <t>Argentina</t>
@@ -119,29 +126,41 @@
     <t>Venezuela</t>
   </si>
   <si>
-    <t>ethnic</t>
+    <t>variables</t>
   </si>
   <si>
-    <t>variable</t>
-  </si>
-  <si>
-    <t>descripcion</t>
+    <t>tipo</t>
   </si>
   <si>
     <t>medicion</t>
   </si>
   <si>
-    <t>min</t>
+    <t>minimo</t>
   </si>
   <si>
-    <t>max</t>
+    <t>maximo</t>
+  </si>
+  <si>
+    <t>continua</t>
+  </si>
+  <si>
+    <t>número de partidos</t>
+  </si>
+  <si>
+    <t>discreta</t>
+  </si>
+  <si>
+    <t>tamaño asamblea</t>
+  </si>
+  <si>
+    <t>tamaño distrito</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -275,6 +294,20 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="38">
@@ -488,7 +521,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -603,6 +636,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -648,17 +696,20 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1015,18 +1066,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D72FA4F-E2D9-42B9-809F-A6413EE8998C}">
   <dimension ref="A1:I199"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" customWidth="1"/>
     <col min="4" max="5" width="10.83203125" customWidth="1"/>
     <col min="6" max="6" width="11.5" style="4"/>
     <col min="7" max="7" width="11.5" style="2"/>
     <col min="8" max="8" width="11.5" style="1"/>
-    <col min="9" max="9" width="11.5" style="3"/>
+    <col min="9" max="9" width="11.5" style="3" customWidth="1"/>
+    <col min="13" max="13" width="8.83203125" customWidth="1"/>
+    <col min="14" max="14" width="9.33203125" customWidth="1"/>
+    <col min="15" max="15" width="22" customWidth="1"/>
+    <col min="16" max="16" width="30.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1042,22 +1097,22 @@
       <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>6</v>
-      </c>
       <c r="I1" s="5" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1072,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="4">
-        <v>1</v>
+        <v>2.63</v>
       </c>
       <c r="G2" s="2">
         <v>254</v>
@@ -1086,7 +1141,7 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -1101,7 +1156,7 @@
         <v>2</v>
       </c>
       <c r="F3" s="4">
-        <v>2</v>
+        <v>3.74</v>
       </c>
       <c r="G3" s="2">
         <v>254</v>
@@ -1115,7 +1170,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -1130,7 +1185,7 @@
         <v>4</v>
       </c>
       <c r="F4" s="4">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="G4" s="2">
         <v>254</v>
@@ -1144,7 +1199,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -1159,7 +1214,7 @@
         <v>6</v>
       </c>
       <c r="F5" s="4">
-        <v>4</v>
+        <v>3.32</v>
       </c>
       <c r="G5" s="2">
         <v>254</v>
@@ -1173,7 +1228,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6">
         <v>1</v>
@@ -1188,7 +1243,7 @@
         <v>8</v>
       </c>
       <c r="F6" s="4">
-        <v>5</v>
+        <v>3.87</v>
       </c>
       <c r="G6" s="2">
         <v>254</v>
@@ -1202,7 +1257,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7">
         <v>1</v>
@@ -1217,7 +1272,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="4">
-        <v>6</v>
+        <v>3.48</v>
       </c>
       <c r="G7" s="2">
         <v>257</v>
@@ -1231,7 +1286,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -1246,7 +1301,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="4">
-        <v>7</v>
+        <v>3.42</v>
       </c>
       <c r="G8" s="2">
         <v>257</v>
@@ -1260,7 +1315,7 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -1275,7 +1330,7 @@
         <v>14</v>
       </c>
       <c r="F9" s="4">
-        <v>8</v>
+        <v>2.82</v>
       </c>
       <c r="G9" s="2">
         <v>257</v>
@@ -1289,7 +1344,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -1304,7 +1359,7 @@
         <v>16</v>
       </c>
       <c r="F10" s="4">
-        <v>9</v>
+        <v>2.72</v>
       </c>
       <c r="G10" s="2">
         <v>257</v>
@@ -1318,7 +1373,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -1333,7 +1388,7 @@
         <v>18</v>
       </c>
       <c r="F11" s="4">
-        <v>10</v>
+        <v>4.68</v>
       </c>
       <c r="G11" s="2">
         <v>257</v>
@@ -1347,7 +1402,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -1362,7 +1417,7 @@
         <v>20</v>
       </c>
       <c r="F12" s="4">
-        <v>11</v>
+        <v>5.16</v>
       </c>
       <c r="G12" s="2">
         <v>257</v>
@@ -1376,7 +1431,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -1391,7 +1446,7 @@
         <v>22</v>
       </c>
       <c r="F13" s="4">
-        <v>12</v>
+        <v>5.22</v>
       </c>
       <c r="G13" s="2">
         <v>257</v>
@@ -1405,7 +1460,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -1420,7 +1475,7 @@
         <v>24</v>
       </c>
       <c r="F14" s="4">
-        <v>13</v>
+        <v>3.48</v>
       </c>
       <c r="G14" s="2">
         <v>257</v>
@@ -1434,7 +1489,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -1449,7 +1504,7 @@
         <v>26</v>
       </c>
       <c r="F15" s="4">
-        <v>14</v>
+        <v>4.92</v>
       </c>
       <c r="G15" s="2">
         <v>257</v>
@@ -1463,7 +1518,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -1478,7 +1533,7 @@
         <v>28</v>
       </c>
       <c r="F16" s="4">
-        <v>15</v>
+        <v>3.11</v>
       </c>
       <c r="G16" s="2">
         <v>257</v>
@@ -1492,7 +1547,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -1507,7 +1562,7 @@
         <v>30</v>
       </c>
       <c r="F17" s="4">
-        <v>16</v>
+        <v>4.74</v>
       </c>
       <c r="G17" s="2">
         <v>257</v>
@@ -1521,7 +1576,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -1536,7 +1591,7 @@
         <v>32</v>
       </c>
       <c r="F18" s="4">
-        <v>17</v>
+        <v>3.37</v>
       </c>
       <c r="G18" s="2">
         <v>257</v>
@@ -1550,7 +1605,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -1565,7 +1620,7 @@
         <v>34</v>
       </c>
       <c r="F19" s="4">
-        <v>18</v>
+        <v>3.8</v>
       </c>
       <c r="G19" s="2">
         <v>257</v>
@@ -1579,7 +1634,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -1594,7 +1649,7 @@
         <v>36</v>
       </c>
       <c r="F20" s="4">
-        <v>19</v>
+        <v>2.72</v>
       </c>
       <c r="G20" s="2">
         <v>257</v>
@@ -1608,7 +1663,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -1623,7 +1678,7 @@
         <v>38</v>
       </c>
       <c r="F21" s="4">
-        <v>20</v>
+        <v>3.19</v>
       </c>
       <c r="G21" s="2">
         <v>257</v>
@@ -1637,7 +1692,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B22">
         <v>2</v>
@@ -1652,7 +1707,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="4">
-        <v>1</v>
+        <v>3.51</v>
       </c>
       <c r="G22" s="2">
         <v>102</v>
@@ -1666,7 +1721,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B23">
         <v>2</v>
@@ -1681,7 +1736,7 @@
         <v>1</v>
       </c>
       <c r="F23" s="4">
-        <v>2</v>
+        <v>4.66</v>
       </c>
       <c r="G23" s="2">
         <v>130</v>
@@ -1695,7 +1750,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B24">
         <v>2</v>
@@ -1710,7 +1765,7 @@
         <v>6</v>
       </c>
       <c r="F24" s="4">
-        <v>3</v>
+        <v>4.58</v>
       </c>
       <c r="G24" s="2">
         <v>130</v>
@@ -1724,7 +1779,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B25">
         <v>2</v>
@@ -1739,7 +1794,7 @@
         <v>10</v>
       </c>
       <c r="F25" s="4">
-        <v>4</v>
+        <v>5.05</v>
       </c>
       <c r="G25" s="2">
         <v>130</v>
@@ -1753,7 +1808,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B26">
         <v>2</v>
@@ -1768,7 +1823,7 @@
         <v>14</v>
       </c>
       <c r="F26" s="4">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="G26" s="2">
         <v>130</v>
@@ -1782,7 +1837,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -1797,7 +1852,7 @@
         <v>18</v>
       </c>
       <c r="F27" s="4">
-        <v>6</v>
+        <v>6.16</v>
       </c>
       <c r="G27" s="2">
         <v>130</v>
@@ -1811,7 +1866,7 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B28">
         <v>2</v>
@@ -1826,7 +1881,7 @@
         <v>23</v>
       </c>
       <c r="F28" s="4">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="G28" s="2">
         <v>130</v>
@@ -1840,7 +1895,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B29">
         <v>2</v>
@@ -1855,7 +1910,7 @@
         <v>26</v>
       </c>
       <c r="F29" s="4">
-        <v>8</v>
+        <v>2.95</v>
       </c>
       <c r="G29" s="2">
         <v>130</v>
@@ -1869,7 +1924,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B30">
         <v>2</v>
@@ -1884,7 +1939,7 @@
         <v>30</v>
       </c>
       <c r="F30" s="4">
-        <v>9</v>
+        <v>2.23</v>
       </c>
       <c r="G30" s="2">
         <v>130</v>
@@ -1898,7 +1953,7 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B31">
         <v>2</v>
@@ -1913,7 +1968,7 @@
         <v>35</v>
       </c>
       <c r="F31" s="4">
-        <v>10</v>
+        <v>2.48</v>
       </c>
       <c r="G31" s="2">
         <v>130</v>
@@ -1927,7 +1982,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B32">
         <v>2</v>
@@ -1942,7 +1997,7 @@
         <v>41</v>
       </c>
       <c r="F32" s="4">
-        <v>11</v>
+        <v>2.57</v>
       </c>
       <c r="G32" s="2">
         <v>130</v>
@@ -1956,7 +2011,7 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B33">
         <v>3</v>
@@ -1971,7 +2026,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="4">
-        <v>1</v>
+        <v>3.56</v>
       </c>
       <c r="G33" s="2">
         <v>487</v>
@@ -1985,7 +2040,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B34">
         <v>3</v>
@@ -2000,7 +2055,7 @@
         <v>4</v>
       </c>
       <c r="F34" s="4">
-        <v>2</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="G34" s="2">
         <v>503</v>
@@ -2014,7 +2069,7 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B35">
         <v>3</v>
@@ -2029,7 +2084,7 @@
         <v>8</v>
       </c>
       <c r="F35" s="4">
-        <v>3</v>
+        <v>8.52</v>
       </c>
       <c r="G35" s="2">
         <v>513</v>
@@ -2043,7 +2098,7 @@
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B36">
         <v>3</v>
@@ -2058,7 +2113,7 @@
         <v>12</v>
       </c>
       <c r="F36" s="4">
-        <v>4</v>
+        <v>8.14</v>
       </c>
       <c r="G36" s="2">
         <v>513</v>
@@ -2072,7 +2127,7 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B37">
         <v>3</v>
@@ -2087,7 +2142,7 @@
         <v>16</v>
       </c>
       <c r="F37" s="4">
-        <v>5</v>
+        <v>9.2899999999999991</v>
       </c>
       <c r="G37" s="2">
         <v>513</v>
@@ -2101,7 +2156,7 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B38">
         <v>3</v>
@@ -2116,7 +2171,7 @@
         <v>20</v>
       </c>
       <c r="F38" s="4">
-        <v>6</v>
+        <v>10.62</v>
       </c>
       <c r="G38" s="2">
         <v>513</v>
@@ -2130,7 +2185,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B39">
         <v>3</v>
@@ -2145,7 +2200,7 @@
         <v>24</v>
       </c>
       <c r="F39" s="4">
-        <v>7</v>
+        <v>11.21</v>
       </c>
       <c r="G39" s="2">
         <v>513</v>
@@ -2159,7 +2214,7 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B40">
         <v>3</v>
@@ -2174,7 +2229,7 @@
         <v>28</v>
       </c>
       <c r="F40" s="4">
-        <v>8</v>
+        <v>14.1</v>
       </c>
       <c r="G40" s="2">
         <v>513</v>
@@ -2188,7 +2243,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B41">
         <v>3</v>
@@ -2203,7 +2258,7 @@
         <v>32</v>
       </c>
       <c r="F41" s="4">
-        <v>9</v>
+        <v>18.010000000000002</v>
       </c>
       <c r="G41" s="2">
         <v>513</v>
@@ -2217,7 +2272,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B42">
         <v>4</v>
@@ -2232,7 +2287,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="4">
-        <v>1</v>
+        <v>2.59</v>
       </c>
       <c r="G42" s="2">
         <v>120</v>
@@ -2246,7 +2301,7 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B43">
         <v>4</v>
@@ -2261,7 +2316,7 @@
         <v>4</v>
       </c>
       <c r="F43" s="4">
-        <v>2</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="G43" s="2">
         <v>120</v>
@@ -2275,7 +2330,7 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B44">
         <v>4</v>
@@ -2290,7 +2345,7 @@
         <v>8</v>
       </c>
       <c r="F44" s="4">
-        <v>3</v>
+        <v>2.54</v>
       </c>
       <c r="G44" s="2">
         <v>120</v>
@@ -2304,7 +2359,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B45">
         <v>4</v>
@@ -2319,7 +2374,7 @@
         <v>12</v>
       </c>
       <c r="F45" s="4">
-        <v>4</v>
+        <v>2.34</v>
       </c>
       <c r="G45" s="2">
         <v>120</v>
@@ -2333,7 +2388,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B46">
         <v>4</v>
@@ -2348,7 +2403,7 @@
         <v>16</v>
       </c>
       <c r="F46" s="4">
-        <v>5</v>
+        <v>2.36</v>
       </c>
       <c r="G46" s="2">
         <v>120</v>
@@ -2362,7 +2417,7 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B47">
         <v>4</v>
@@ -2377,7 +2432,7 @@
         <v>20</v>
       </c>
       <c r="F47" s="4">
-        <v>6</v>
+        <v>2.56</v>
       </c>
       <c r="G47" s="2">
         <v>120</v>
@@ -2391,7 +2446,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B48">
         <v>4</v>
@@ -2406,7 +2461,7 @@
         <v>24</v>
       </c>
       <c r="F48" s="4">
-        <v>7</v>
+        <v>2.75</v>
       </c>
       <c r="G48" s="2">
         <v>120</v>
@@ -2420,7 +2475,7 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B49">
         <v>4</v>
@@ -2435,7 +2490,7 @@
         <v>28</v>
       </c>
       <c r="F49" s="4">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="G49" s="2">
         <v>155</v>
@@ -2449,7 +2504,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B50">
         <v>4</v>
@@ -2464,7 +2519,7 @@
         <v>32</v>
       </c>
       <c r="F50" s="4">
-        <v>9</v>
+        <v>6.1</v>
       </c>
       <c r="G50" s="2">
         <v>155</v>
@@ -2478,7 +2533,7 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B51">
         <v>5</v>
@@ -2493,7 +2548,7 @@
         <v>12</v>
       </c>
       <c r="F51" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G51" s="2">
         <v>210</v>
@@ -2507,7 +2562,7 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B52">
         <v>5</v>
@@ -2522,7 +2577,7 @@
         <v>16</v>
       </c>
       <c r="F52" s="4">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="G52" s="2">
         <v>199</v>
@@ -2536,7 +2591,7 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B53">
         <v>5</v>
@@ -2551,7 +2606,7 @@
         <v>20</v>
       </c>
       <c r="F53" s="4">
-        <v>3</v>
+        <v>2.17</v>
       </c>
       <c r="G53" s="2">
         <v>199</v>
@@ -2565,7 +2620,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B54">
         <v>5</v>
@@ -2580,7 +2635,7 @@
         <v>24</v>
       </c>
       <c r="F54" s="4">
-        <v>4</v>
+        <v>2.08</v>
       </c>
       <c r="G54" s="2">
         <v>199</v>
@@ -2594,7 +2649,7 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B55">
         <v>5</v>
@@ -2609,7 +2664,7 @@
         <v>28</v>
       </c>
       <c r="F55" s="4">
-        <v>5</v>
+        <v>2.66</v>
       </c>
       <c r="G55" s="2">
         <v>199</v>
@@ -2623,7 +2678,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B56">
         <v>5</v>
@@ -2638,7 +2693,7 @@
         <v>32</v>
       </c>
       <c r="F56" s="4">
-        <v>6</v>
+        <v>2.21</v>
       </c>
       <c r="G56" s="2">
         <v>199</v>
@@ -2652,7 +2707,7 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B57">
         <v>5</v>
@@ -2667,7 +2722,7 @@
         <v>33</v>
       </c>
       <c r="F57" s="4">
-        <v>7</v>
+        <v>3.32</v>
       </c>
       <c r="G57" s="2">
         <v>161</v>
@@ -2681,7 +2736,7 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B58">
         <v>5</v>
@@ -2696,7 +2751,7 @@
         <v>36</v>
       </c>
       <c r="F58" s="4">
-        <v>8</v>
+        <v>3.14</v>
       </c>
       <c r="G58" s="2">
         <v>162</v>
@@ -2710,7 +2765,7 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B59">
         <v>5</v>
@@ -2725,7 +2780,7 @@
         <v>40</v>
       </c>
       <c r="F59" s="4">
-        <v>9</v>
+        <v>3.6</v>
       </c>
       <c r="G59" s="2">
         <v>161</v>
@@ -2739,7 +2794,7 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B60">
         <v>5</v>
@@ -2754,7 +2809,7 @@
         <v>44</v>
       </c>
       <c r="F60" s="4">
-        <v>10</v>
+        <v>9.75</v>
       </c>
       <c r="G60" s="2">
         <v>161</v>
@@ -2768,7 +2823,7 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B61">
         <v>5</v>
@@ -2783,7 +2838,7 @@
         <v>48</v>
       </c>
       <c r="F61" s="4">
-        <v>11</v>
+        <v>8.66</v>
       </c>
       <c r="G61" s="2">
         <v>166</v>
@@ -2797,7 +2852,7 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B62">
         <v>5</v>
@@ -2812,7 +2867,7 @@
         <v>52</v>
       </c>
       <c r="F62" s="4">
-        <v>12</v>
+        <v>5.96</v>
       </c>
       <c r="G62" s="2">
         <v>164</v>
@@ -2826,7 +2881,7 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B63">
         <v>5</v>
@@ -2841,7 +2896,7 @@
         <v>56</v>
       </c>
       <c r="F63" s="4">
-        <v>13</v>
+        <v>7.36</v>
       </c>
       <c r="G63" s="2">
         <v>166</v>
@@ -2855,7 +2910,7 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B64">
         <v>5</v>
@@ -2870,7 +2925,7 @@
         <v>60</v>
       </c>
       <c r="F64" s="4">
-        <v>14</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="G64" s="2">
         <v>167</v>
@@ -2884,7 +2939,7 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B65">
         <v>6</v>
@@ -2899,7 +2954,7 @@
         <v>0</v>
       </c>
       <c r="F65" s="4">
-        <v>1</v>
+        <v>1.96</v>
       </c>
       <c r="G65" s="2">
         <v>45</v>
@@ -2913,7 +2968,7 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B66">
         <v>6</v>
@@ -2928,7 +2983,7 @@
         <v>4</v>
       </c>
       <c r="F66" s="4">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="G66" s="2">
         <v>45</v>
@@ -2942,7 +2997,7 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B67">
         <v>6</v>
@@ -2957,7 +3012,7 @@
         <v>9</v>
       </c>
       <c r="F67" s="4">
-        <v>3</v>
+        <v>3.57</v>
       </c>
       <c r="G67" s="2">
         <v>45</v>
@@ -2971,7 +3026,7 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B68">
         <v>6</v>
@@ -2986,7 +3041,7 @@
         <v>13</v>
       </c>
       <c r="F68" s="4">
-        <v>4</v>
+        <v>2.71</v>
       </c>
       <c r="G68" s="2">
         <v>57</v>
@@ -3000,7 +3055,7 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B69">
         <v>6</v>
@@ -3015,7 +3070,7 @@
         <v>17</v>
       </c>
       <c r="F69" s="4">
-        <v>5</v>
+        <v>2.33</v>
       </c>
       <c r="G69" s="2">
         <v>57</v>
@@ -3029,7 +3084,7 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B70">
         <v>6</v>
@@ -3044,7 +3099,7 @@
         <v>21</v>
       </c>
       <c r="F70" s="4">
-        <v>6</v>
+        <v>2.56</v>
       </c>
       <c r="G70" s="2">
         <v>57</v>
@@ -3058,7 +3113,7 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B71">
         <v>6</v>
@@ -3073,7 +3128,7 @@
         <v>25</v>
       </c>
       <c r="F71" s="4">
-        <v>7</v>
+        <v>4.01</v>
       </c>
       <c r="G71" s="2">
         <v>57</v>
@@ -3087,7 +3142,7 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B72">
         <v>6</v>
@@ -3102,7 +3157,7 @@
         <v>29</v>
       </c>
       <c r="F72" s="4">
-        <v>8</v>
+        <v>2.88</v>
       </c>
       <c r="G72" s="2">
         <v>57</v>
@@ -3116,7 +3171,7 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B73">
         <v>6</v>
@@ -3131,7 +3186,7 @@
         <v>33</v>
       </c>
       <c r="F73" s="4">
-        <v>9</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="G73" s="2">
         <v>57</v>
@@ -3145,7 +3200,7 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B74">
         <v>6</v>
@@ -3160,7 +3215,7 @@
         <v>37</v>
       </c>
       <c r="F74" s="4">
-        <v>10</v>
+        <v>2.48</v>
       </c>
       <c r="G74" s="2">
         <v>57</v>
@@ -3174,7 +3229,7 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B75">
         <v>6</v>
@@ -3189,7 +3244,7 @@
         <v>41</v>
       </c>
       <c r="F75" s="4">
-        <v>11</v>
+        <v>2.48</v>
       </c>
       <c r="G75" s="2">
         <v>57</v>
@@ -3203,7 +3258,7 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B76">
         <v>6</v>
@@ -3218,7 +3273,7 @@
         <v>45</v>
       </c>
       <c r="F76" s="4">
-        <v>12</v>
+        <v>2.61</v>
       </c>
       <c r="G76" s="2">
         <v>57</v>
@@ -3232,7 +3287,7 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B77">
         <v>6</v>
@@ -3247,7 +3302,7 @@
         <v>49</v>
       </c>
       <c r="F77" s="4">
-        <v>13</v>
+        <v>3.12</v>
       </c>
       <c r="G77" s="2">
         <v>57</v>
@@ -3261,7 +3316,7 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B78">
         <v>6</v>
@@ -3276,7 +3331,7 @@
         <v>53</v>
       </c>
       <c r="F78" s="4">
-        <v>14</v>
+        <v>4.45</v>
       </c>
       <c r="G78" s="2">
         <v>57</v>
@@ -3290,7 +3345,7 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B79">
         <v>6</v>
@@ -3305,7 +3360,7 @@
         <v>57</v>
       </c>
       <c r="F79" s="4">
-        <v>15</v>
+        <v>4.62</v>
       </c>
       <c r="G79" s="2">
         <v>57</v>
@@ -3319,7 +3374,7 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B80">
         <v>6</v>
@@ -3334,7 +3389,7 @@
         <v>61</v>
       </c>
       <c r="F80" s="4">
-        <v>16</v>
+        <v>4.34</v>
       </c>
       <c r="G80" s="2">
         <v>57</v>
@@ -3348,7 +3403,7 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B81">
         <v>6</v>
@@ -3363,7 +3418,7 @@
         <v>65</v>
       </c>
       <c r="F81" s="4">
-        <v>17</v>
+        <v>6.09</v>
       </c>
       <c r="G81" s="2">
         <v>57</v>
@@ -3377,7 +3432,7 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B82">
         <v>6</v>
@@ -3392,7 +3447,7 @@
         <v>69</v>
       </c>
       <c r="F82" s="4">
-        <v>18</v>
+        <v>7.59</v>
       </c>
       <c r="G82" s="2">
         <v>57</v>
@@ -3406,7 +3461,7 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B83">
         <v>7</v>
@@ -3421,7 +3476,7 @@
         <v>8</v>
       </c>
       <c r="F83" s="4">
-        <v>1</v>
+        <v>1.23</v>
       </c>
       <c r="G83" s="2">
         <v>91</v>
@@ -3435,7 +3490,7 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B84">
         <v>7</v>
@@ -3450,7 +3505,7 @@
         <v>12</v>
       </c>
       <c r="F84" s="4">
-        <v>2</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="G84" s="2">
         <v>91</v>
@@ -3464,7 +3519,7 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B85">
         <v>7</v>
@@ -3479,7 +3534,7 @@
         <v>16</v>
       </c>
       <c r="F85" s="4">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="G85" s="2">
         <v>120</v>
@@ -3493,7 +3548,7 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B86">
         <v>7</v>
@@ -3508,7 +3563,7 @@
         <v>20</v>
       </c>
       <c r="F86" s="4">
-        <v>4</v>
+        <v>3.19</v>
       </c>
       <c r="G86" s="2">
         <v>120</v>
@@ -3522,7 +3577,7 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B87">
         <v>7</v>
@@ -3537,7 +3592,7 @@
         <v>24</v>
       </c>
       <c r="F87" s="4">
-        <v>5</v>
+        <v>3.67</v>
       </c>
       <c r="G87" s="2">
         <v>120</v>
@@ -3551,7 +3606,7 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B88">
         <v>7</v>
@@ -3566,7 +3621,7 @@
         <v>28</v>
       </c>
       <c r="F88" s="4">
-        <v>6</v>
+        <v>3.01</v>
       </c>
       <c r="G88" s="2">
         <v>120</v>
@@ -3580,7 +3635,7 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B89">
         <v>7</v>
@@ -3595,7 +3650,7 @@
         <v>32</v>
       </c>
       <c r="F89" s="4">
-        <v>7</v>
+        <v>2.74</v>
       </c>
       <c r="G89" s="2">
         <v>149</v>
@@ -3609,7 +3664,7 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B90">
         <v>7</v>
@@ -3624,7 +3679,7 @@
         <v>36</v>
       </c>
       <c r="F90" s="4">
-        <v>8</v>
+        <v>3.33</v>
       </c>
       <c r="G90" s="2">
         <v>150</v>
@@ -3638,7 +3693,7 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B91">
         <v>7</v>
@@ -3653,7 +3708,7 @@
         <v>40</v>
       </c>
       <c r="F91" s="4">
-        <v>9</v>
+        <v>3.07</v>
       </c>
       <c r="G91" s="2">
         <v>178</v>
@@ -3667,7 +3722,7 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B92">
         <v>7</v>
@@ -3682,7 +3737,7 @@
         <v>44</v>
       </c>
       <c r="F92" s="4">
-        <v>10</v>
+        <v>3.06</v>
       </c>
       <c r="G92" s="2">
         <v>178</v>
@@ -3696,7 +3751,7 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B93">
         <v>7</v>
@@ -3711,7 +3766,7 @@
         <v>50</v>
       </c>
       <c r="F93" s="4">
-        <v>11</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="G93" s="2">
         <v>190</v>
@@ -3725,7 +3780,7 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B94">
         <v>7</v>
@@ -3740,7 +3795,7 @@
         <v>54</v>
       </c>
       <c r="F94" s="4">
-        <v>12</v>
+        <v>3.63</v>
       </c>
       <c r="G94" s="2">
         <v>190</v>
@@ -3754,7 +3809,7 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B95">
         <v>8</v>
@@ -3769,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="F95" s="4">
-        <v>1</v>
+        <v>6.1</v>
       </c>
       <c r="G95" s="2">
         <v>69</v>
@@ -3783,7 +3838,7 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B96">
         <v>8</v>
@@ -3798,7 +3853,7 @@
         <v>5</v>
       </c>
       <c r="F96" s="4">
-        <v>2</v>
+        <v>9.89</v>
       </c>
       <c r="G96" s="2">
         <v>71</v>
@@ -3812,7 +3867,7 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B97">
         <v>8</v>
@@ -3827,7 +3882,7 @@
         <v>7</v>
       </c>
       <c r="F97" s="4">
-        <v>3</v>
+        <v>11.38</v>
       </c>
       <c r="G97" s="2">
         <v>71</v>
@@ -3841,7 +3896,7 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B98">
         <v>8</v>
@@ -3856,7 +3911,7 @@
         <v>9</v>
       </c>
       <c r="F98" s="4">
-        <v>4</v>
+        <v>8.49</v>
       </c>
       <c r="G98" s="2">
         <v>71</v>
@@ -3870,7 +3925,7 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B99">
         <v>8</v>
@@ -3885,7 +3940,7 @@
         <v>11</v>
       </c>
       <c r="F99" s="4">
-        <v>5</v>
+        <v>7.88</v>
       </c>
       <c r="G99" s="2">
         <v>71</v>
@@ -3899,7 +3954,7 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B100">
         <v>8</v>
@@ -3914,7 +3969,7 @@
         <v>13</v>
       </c>
       <c r="F100" s="4">
-        <v>6</v>
+        <v>7.65</v>
       </c>
       <c r="G100" s="2">
         <v>77</v>
@@ -3928,7 +3983,7 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B101">
         <v>8</v>
@@ -3943,7 +3998,7 @@
         <v>15</v>
       </c>
       <c r="F101" s="4">
-        <v>7</v>
+        <v>7.48</v>
       </c>
       <c r="G101" s="2">
         <v>77</v>
@@ -3957,7 +4012,7 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B102">
         <v>8</v>
@@ -3972,7 +4027,7 @@
         <v>17</v>
       </c>
       <c r="F102" s="4">
-        <v>8</v>
+        <v>6.21</v>
       </c>
       <c r="G102" s="2">
         <v>82</v>
@@ -3986,7 +4041,7 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B103">
         <v>8</v>
@@ -4001,7 +4056,7 @@
         <v>19</v>
       </c>
       <c r="F103" s="4">
-        <v>9</v>
+        <v>6.64</v>
       </c>
       <c r="G103" s="2">
         <v>121</v>
@@ -4015,7 +4070,7 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B104">
         <v>8</v>
@@ -4030,7 +4085,7 @@
         <v>23</v>
       </c>
       <c r="F104" s="4">
-        <v>10</v>
+        <v>9.31</v>
       </c>
       <c r="G104" s="2">
         <v>100</v>
@@ -4044,7 +4099,7 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B105">
         <v>8</v>
@@ -4059,7 +4114,7 @@
         <v>27</v>
       </c>
       <c r="F105" s="4">
-        <v>11</v>
+        <v>8.01</v>
       </c>
       <c r="G105" s="2">
         <v>100</v>
@@ -4073,7 +4128,7 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B106">
         <v>8</v>
@@ -4088,7 +4143,7 @@
         <v>30</v>
       </c>
       <c r="F106" s="4">
-        <v>12</v>
+        <v>4.21</v>
       </c>
       <c r="G106" s="2">
         <v>124</v>
@@ -4102,7 +4157,7 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B107">
         <v>8</v>
@@ -4117,7 +4172,7 @@
         <v>34</v>
       </c>
       <c r="F107" s="4">
-        <v>13</v>
+        <v>3.27</v>
       </c>
       <c r="G107" s="2">
         <v>137</v>
@@ -4131,7 +4186,7 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B108">
         <v>8</v>
@@ -4146,7 +4201,7 @@
         <v>38</v>
       </c>
       <c r="F108" s="4">
-        <v>14</v>
+        <v>4.68</v>
       </c>
       <c r="G108" s="2">
         <v>137</v>
@@ -4160,7 +4215,7 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B109">
         <v>8</v>
@@ -4175,7 +4230,7 @@
         <v>42</v>
       </c>
       <c r="F109" s="4">
-        <v>15</v>
+        <v>6.88</v>
       </c>
       <c r="G109" s="2">
         <v>137</v>
@@ -4189,7 +4244,7 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B110">
         <v>9</v>
@@ -4204,7 +4259,7 @@
         <v>0</v>
       </c>
       <c r="F110" s="4">
-        <v>1</v>
+        <v>2.69</v>
       </c>
       <c r="G110" s="2">
         <v>60</v>
@@ -4218,7 +4273,7 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B111">
         <v>9</v>
@@ -4233,7 +4288,7 @@
         <v>3</v>
       </c>
       <c r="F111" s="4">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="G111" s="2">
         <v>60</v>
@@ -4247,7 +4302,7 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B112">
         <v>9</v>
@@ -4262,7 +4317,7 @@
         <v>6</v>
       </c>
       <c r="F112" s="4">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="G112" s="2">
         <v>84</v>
@@ -4276,7 +4331,7 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B113">
         <v>9</v>
@@ -4291,7 +4346,7 @@
         <v>9</v>
       </c>
       <c r="F113" s="4">
-        <v>4</v>
+        <v>3.48</v>
       </c>
       <c r="G113" s="2">
         <v>84</v>
@@ -4305,7 +4360,7 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B114">
         <v>9</v>
@@ -4320,7 +4375,7 @@
         <v>12</v>
       </c>
       <c r="F114" s="4">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="G114" s="2">
         <v>84</v>
@@ -4334,7 +4389,7 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B115">
         <v>9</v>
@@ -4349,7 +4404,7 @@
         <v>15</v>
       </c>
       <c r="F115" s="4">
-        <v>6</v>
+        <v>3.68</v>
       </c>
       <c r="G115" s="2">
         <v>84</v>
@@ -4363,7 +4418,7 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B116">
         <v>9</v>
@@ -4378,7 +4433,7 @@
         <v>18</v>
       </c>
       <c r="F116" s="4">
-        <v>7</v>
+        <v>4.09</v>
       </c>
       <c r="G116" s="2">
         <v>84</v>
@@ -4392,7 +4447,7 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B117">
         <v>9</v>
@@ -4407,7 +4462,7 @@
         <v>21</v>
       </c>
       <c r="F117" s="4">
-        <v>8</v>
+        <v>3.06</v>
       </c>
       <c r="G117" s="2">
         <v>84</v>
@@ -4421,7 +4476,7 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B118">
         <v>9</v>
@@ -4436,7 +4491,7 @@
         <v>24</v>
       </c>
       <c r="F118" s="4">
-        <v>9</v>
+        <v>2.91</v>
       </c>
       <c r="G118" s="2">
         <v>84</v>
@@ -4450,7 +4505,7 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B119">
         <v>9</v>
@@ -4465,7 +4520,7 @@
         <v>27</v>
       </c>
       <c r="F119" s="4">
-        <v>10</v>
+        <v>3.24</v>
       </c>
       <c r="G119" s="2">
         <v>84</v>
@@ -4479,7 +4534,7 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B120">
         <v>9</v>
@@ -4494,7 +4549,7 @@
         <v>30</v>
       </c>
       <c r="F120" s="4">
-        <v>11</v>
+        <v>3.15</v>
       </c>
       <c r="G120" s="2">
         <v>84</v>
@@ -4508,7 +4563,7 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B121">
         <v>9</v>
@@ -4523,7 +4578,7 @@
         <v>33</v>
       </c>
       <c r="F121" s="4">
-        <v>12</v>
+        <v>3.34</v>
       </c>
       <c r="G121" s="2">
         <v>84</v>
@@ -4537,7 +4592,7 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B122">
         <v>9</v>
@@ -4552,7 +4607,7 @@
         <v>36</v>
       </c>
       <c r="F122" s="4">
-        <v>13</v>
+        <v>2.72</v>
       </c>
       <c r="G122" s="2">
         <v>84</v>
@@ -4566,7 +4621,7 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B123">
         <v>10</v>
@@ -4581,7 +4636,7 @@
         <v>0</v>
       </c>
       <c r="F123" s="4">
-        <v>1</v>
+        <v>4.53</v>
       </c>
       <c r="G123" s="2">
         <v>100</v>
@@ -4595,7 +4650,7 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B124">
         <v>10</v>
@@ -4610,7 +4665,7 @@
         <v>5</v>
       </c>
       <c r="F124" s="4">
-        <v>2</v>
+        <v>6.37</v>
       </c>
       <c r="G124" s="2">
         <v>116</v>
@@ -4624,7 +4679,7 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B125">
         <v>10</v>
@@ -4639,7 +4694,7 @@
         <v>10</v>
       </c>
       <c r="F125" s="4">
-        <v>3</v>
+        <v>5.42</v>
       </c>
       <c r="G125" s="2">
         <v>80</v>
@@ -4653,7 +4708,7 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B126">
         <v>10</v>
@@ -4668,7 +4723,7 @@
         <v>14</v>
       </c>
       <c r="F126" s="4">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="G126" s="2">
         <v>113</v>
@@ -4682,7 +4737,7 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B127">
         <v>10</v>
@@ -4697,7 +4752,7 @@
         <v>18</v>
       </c>
       <c r="F127" s="4">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="G127" s="2">
         <v>158</v>
@@ -4711,7 +4766,7 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B128">
         <v>10</v>
@@ -4726,7 +4781,7 @@
         <v>22</v>
       </c>
       <c r="F128" s="4">
-        <v>6</v>
+        <v>7.57</v>
       </c>
       <c r="G128" s="2">
         <v>158</v>
@@ -4740,7 +4795,7 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B129">
         <v>10</v>
@@ -4755,7 +4810,7 @@
         <v>26</v>
       </c>
       <c r="F129" s="4">
-        <v>7</v>
+        <v>6.98</v>
       </c>
       <c r="G129" s="2">
         <v>158</v>
@@ -4769,7 +4824,7 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B130">
         <v>10</v>
@@ -4784,7 +4839,7 @@
         <v>30</v>
       </c>
       <c r="F130" s="4">
-        <v>8</v>
+        <v>9.91</v>
       </c>
       <c r="G130" s="2">
         <v>158</v>
@@ -4798,7 +4853,7 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B131">
         <v>10</v>
@@ -4813,7 +4868,7 @@
         <v>34</v>
       </c>
       <c r="F131" s="4">
-        <v>9</v>
+        <v>13.33</v>
       </c>
       <c r="G131" s="2">
         <v>160</v>
@@ -4827,7 +4882,7 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B132">
         <v>11</v>
@@ -4842,7 +4897,7 @@
         <v>0</v>
       </c>
       <c r="F132" s="4">
-        <v>1</v>
+        <v>2.15</v>
       </c>
       <c r="G132" s="2">
         <v>82</v>
@@ -4856,7 +4911,7 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B133">
         <v>11</v>
@@ -4871,7 +4926,7 @@
         <v>4</v>
       </c>
       <c r="F133" s="4">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="G133" s="2">
         <v>134</v>
@@ -4885,7 +4940,7 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B134">
         <v>11</v>
@@ -4900,7 +4955,7 @@
         <v>8</v>
       </c>
       <c r="F134" s="4">
-        <v>3</v>
+        <v>2.13</v>
       </c>
       <c r="G134" s="2">
         <v>128</v>
@@ -4914,7 +4969,7 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B135">
         <v>11</v>
@@ -4929,7 +4984,7 @@
         <v>12</v>
       </c>
       <c r="F135" s="4">
-        <v>4</v>
+        <v>2.14</v>
       </c>
       <c r="G135" s="2">
         <v>128</v>
@@ -4943,7 +4998,7 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B136">
         <v>11</v>
@@ -4958,7 +5013,7 @@
         <v>16</v>
       </c>
       <c r="F136" s="4">
-        <v>5</v>
+        <v>2.37</v>
       </c>
       <c r="G136" s="2">
         <v>128</v>
@@ -4972,7 +5027,7 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B137">
         <v>11</v>
@@ -4987,7 +5042,7 @@
         <v>20</v>
       </c>
       <c r="F137" s="4">
-        <v>6</v>
+        <v>2.58</v>
       </c>
       <c r="G137" s="2">
         <v>128</v>
@@ -5001,7 +5056,7 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B138">
         <v>11</v>
@@ -5016,7 +5071,7 @@
         <v>24</v>
       </c>
       <c r="F138" s="4">
-        <v>7</v>
+        <v>2.69</v>
       </c>
       <c r="G138" s="2">
         <v>128</v>
@@ -5030,7 +5085,7 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B139">
         <v>11</v>
@@ -5045,7 +5100,7 @@
         <v>28</v>
       </c>
       <c r="F139" s="4">
-        <v>8</v>
+        <v>2.46</v>
       </c>
       <c r="G139" s="2">
         <v>128</v>
@@ -5059,7 +5114,7 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B140">
         <v>11</v>
@@ -5074,7 +5129,7 @@
         <v>32</v>
       </c>
       <c r="F140" s="4">
-        <v>9</v>
+        <v>4.1399999999999997</v>
       </c>
       <c r="G140" s="2">
         <v>128</v>
@@ -5088,7 +5143,7 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B141">
         <v>11</v>
@@ -5103,7 +5158,7 @@
         <v>36</v>
       </c>
       <c r="F141" s="4">
-        <v>10</v>
+        <v>3.65</v>
       </c>
       <c r="G141" s="2">
         <v>128</v>
@@ -5117,7 +5172,7 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B142">
         <v>11</v>
@@ -5132,7 +5187,7 @@
         <v>40</v>
       </c>
       <c r="F142" s="4">
-        <v>11</v>
+        <v>3.55</v>
       </c>
       <c r="G142" s="2">
         <v>128</v>
@@ -5146,7 +5201,7 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B143">
         <v>12</v>
@@ -5161,7 +5216,7 @@
         <v>0</v>
       </c>
       <c r="F143" s="4">
-        <v>1</v>
+        <v>2.85</v>
       </c>
       <c r="G143" s="2">
         <v>500</v>
@@ -5175,7 +5230,7 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B144">
         <v>12</v>
@@ -5190,7 +5245,7 @@
         <v>3</v>
       </c>
       <c r="F144" s="4">
-        <v>2</v>
+        <v>3.42</v>
       </c>
       <c r="G144" s="2">
         <v>500</v>
@@ -5204,7 +5259,7 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B145">
         <v>12</v>
@@ -5233,7 +5288,7 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B146">
         <v>12</v>
@@ -5248,7 +5303,7 @@
         <v>9</v>
       </c>
       <c r="F146" s="4">
-        <v>4</v>
+        <v>3.19</v>
       </c>
       <c r="G146" s="2">
         <v>500</v>
@@ -5262,7 +5317,7 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B147">
         <v>12</v>
@@ -5277,7 +5332,7 @@
         <v>12</v>
       </c>
       <c r="F147" s="4">
-        <v>5</v>
+        <v>3.42</v>
       </c>
       <c r="G147" s="2">
         <v>500</v>
@@ -5291,7 +5346,7 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B148">
         <v>12</v>
@@ -5306,7 +5361,7 @@
         <v>15</v>
       </c>
       <c r="F148" s="4">
-        <v>6</v>
+        <v>3.77</v>
       </c>
       <c r="G148" s="2">
         <v>500</v>
@@ -5320,7 +5375,7 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B149">
         <v>12</v>
@@ -5335,7 +5390,7 @@
         <v>18</v>
       </c>
       <c r="F149" s="4">
-        <v>7</v>
+        <v>3.16</v>
       </c>
       <c r="G149" s="2">
         <v>500</v>
@@ -5349,7 +5404,7 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B150">
         <v>12</v>
@@ -5364,7 +5419,7 @@
         <v>21</v>
       </c>
       <c r="F150" s="4">
-        <v>8</v>
+        <v>5.65</v>
       </c>
       <c r="G150" s="2">
         <v>500</v>
@@ -5378,7 +5433,7 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B151">
         <v>12</v>
@@ -5393,7 +5448,7 @@
         <v>24</v>
       </c>
       <c r="F151" s="4">
-        <v>9</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="G151" s="2">
         <v>500</v>
@@ -5407,7 +5462,7 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B152">
         <v>13</v>
@@ -5422,7 +5477,7 @@
         <v>0</v>
       </c>
       <c r="F152" s="4">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="G152" s="2">
         <v>96</v>
@@ -5436,7 +5491,7 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B153">
         <v>13</v>
@@ -5451,7 +5506,7 @@
         <v>6</v>
       </c>
       <c r="F153" s="4">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="G153" s="2">
         <v>90</v>
@@ -5465,7 +5520,7 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B154">
         <v>13</v>
@@ -5480,7 +5535,7 @@
         <v>12</v>
       </c>
       <c r="F154" s="4">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G154" s="2">
         <v>90</v>
@@ -5494,7 +5549,7 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B155">
         <v>13</v>
@@ -5509,7 +5564,7 @@
         <v>17</v>
       </c>
       <c r="F155" s="4">
-        <v>4</v>
+        <v>2.02</v>
       </c>
       <c r="G155" s="2">
         <v>90</v>
@@ -5523,7 +5578,7 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B156">
         <v>13</v>
@@ -5538,7 +5593,7 @@
         <v>22</v>
       </c>
       <c r="F156" s="4">
-        <v>5</v>
+        <v>3.44</v>
       </c>
       <c r="G156" s="2">
         <v>90</v>
@@ -5552,7 +5607,7 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B157">
         <v>13</v>
@@ -5567,7 +5622,7 @@
         <v>27</v>
       </c>
       <c r="F157" s="4">
-        <v>6</v>
+        <v>2.11</v>
       </c>
       <c r="G157" s="2">
         <v>90</v>
@@ -5581,7 +5636,7 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B158">
         <v>13</v>
@@ -5596,7 +5651,7 @@
         <v>32</v>
       </c>
       <c r="F158" s="4">
-        <v>7</v>
+        <v>2.15</v>
       </c>
       <c r="G158" s="2">
         <v>90</v>
@@ -5610,7 +5665,7 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B159">
         <v>14</v>
@@ -5625,7 +5680,7 @@
         <v>0</v>
       </c>
       <c r="F159" s="4">
-        <v>1</v>
+        <v>4.46</v>
       </c>
       <c r="G159" s="2">
         <v>67</v>
@@ -5639,7 +5694,7 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B160">
         <v>14</v>
@@ -5654,7 +5709,7 @@
         <v>5</v>
       </c>
       <c r="F160" s="4">
-        <v>2</v>
+        <v>8.64</v>
       </c>
       <c r="G160" s="2">
         <v>72</v>
@@ -5668,7 +5723,7 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B161">
         <v>14</v>
@@ -5683,7 +5738,7 @@
         <v>10</v>
       </c>
       <c r="F161" s="4">
-        <v>3</v>
+        <v>5.67</v>
       </c>
       <c r="G161" s="2">
         <v>71</v>
@@ -5697,7 +5752,7 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B162">
         <v>14</v>
@@ -5712,7 +5767,7 @@
         <v>15</v>
       </c>
       <c r="F162" s="4">
-        <v>4</v>
+        <v>4.46</v>
       </c>
       <c r="G162" s="2">
         <v>78</v>
@@ -5726,7 +5781,7 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B163">
         <v>14</v>
@@ -5741,7 +5796,7 @@
         <v>20</v>
       </c>
       <c r="F163" s="4">
-        <v>5</v>
+        <v>4.1500000000000004</v>
       </c>
       <c r="G163" s="2">
         <v>71</v>
@@ -5755,7 +5810,7 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B164">
         <v>14</v>
@@ -5770,7 +5825,7 @@
         <v>25</v>
       </c>
       <c r="F164" s="4">
-        <v>6</v>
+        <v>3.83</v>
       </c>
       <c r="G164" s="2">
         <v>71</v>
@@ -5784,7 +5839,7 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B165">
         <v>14</v>
@@ -5799,7 +5854,7 @@
         <v>30</v>
       </c>
       <c r="F165" s="4">
-        <v>7</v>
+        <v>4.93</v>
       </c>
       <c r="G165" s="2">
         <v>71</v>
@@ -5813,7 +5868,7 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B166">
         <v>15</v>
@@ -5828,7 +5883,7 @@
         <v>0</v>
       </c>
       <c r="F166" s="4">
-        <v>1</v>
+        <v>1.68</v>
       </c>
       <c r="G166" s="2">
         <v>72</v>
@@ -5842,7 +5897,7 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B167">
         <v>15</v>
@@ -5857,7 +5912,7 @@
         <v>4</v>
       </c>
       <c r="F167" s="4">
-        <v>2</v>
+        <v>2.81</v>
       </c>
       <c r="G167" s="2">
         <v>80</v>
@@ -5871,7 +5926,7 @@
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B168">
         <v>15</v>
@@ -5886,7 +5941,7 @@
         <v>9</v>
       </c>
       <c r="F168" s="4">
-        <v>3</v>
+        <v>2.12</v>
       </c>
       <c r="G168" s="2">
         <v>80</v>
@@ -5900,7 +5955,7 @@
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B169">
         <v>15</v>
@@ -5915,7 +5970,7 @@
         <v>14</v>
       </c>
       <c r="F169" s="4">
-        <v>4</v>
+        <v>4.21</v>
       </c>
       <c r="G169" s="2">
         <v>80</v>
@@ -5929,7 +5984,7 @@
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B170">
         <v>15</v>
@@ -5944,7 +5999,7 @@
         <v>19</v>
       </c>
       <c r="F170" s="4">
-        <v>5</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="G170" s="2">
         <v>80</v>
@@ -5958,7 +6013,7 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B171">
         <v>15</v>
@@ -5973,7 +6028,7 @@
         <v>24</v>
       </c>
       <c r="F171" s="4">
-        <v>6</v>
+        <v>3.76</v>
       </c>
       <c r="G171" s="2">
         <v>80</v>
@@ -5987,7 +6042,7 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B172">
         <v>15</v>
@@ -6002,7 +6057,7 @@
         <v>29</v>
       </c>
       <c r="F172" s="4">
-        <v>7</v>
+        <v>4.87</v>
       </c>
       <c r="G172" s="2">
         <v>80</v>
@@ -6016,7 +6071,7 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B173">
         <v>16</v>
@@ -6031,7 +6086,7 @@
         <v>0</v>
       </c>
       <c r="F173" s="4">
-        <v>1</v>
+        <v>4.18</v>
       </c>
       <c r="G173" s="2">
         <v>180</v>
@@ -6045,7 +6100,7 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B174">
         <v>16</v>
@@ -6060,7 +6115,7 @@
         <v>5</v>
       </c>
       <c r="F174" s="4">
-        <v>2</v>
+        <v>3.02</v>
       </c>
       <c r="G174" s="2">
         <v>180</v>
@@ -6074,7 +6129,7 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B175">
         <v>16</v>
@@ -6089,7 +6144,7 @@
         <v>10</v>
       </c>
       <c r="F175" s="4">
-        <v>3</v>
+        <v>5.05</v>
       </c>
       <c r="G175" s="2">
         <v>180</v>
@@ -6103,7 +6158,7 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B176">
         <v>16</v>
@@ -6118,7 +6173,7 @@
         <v>21</v>
       </c>
       <c r="F176" s="4">
-        <v>4</v>
+        <v>6.27</v>
       </c>
       <c r="G176" s="2">
         <v>120</v>
@@ -6132,7 +6187,7 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B177">
         <v>16</v>
@@ -6147,7 +6202,7 @@
         <v>26</v>
       </c>
       <c r="F177" s="4">
-        <v>5</v>
+        <v>6.33</v>
       </c>
       <c r="G177" s="2">
         <v>120</v>
@@ -6161,7 +6216,7 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B178">
         <v>16</v>
@@ -6176,7 +6231,7 @@
         <v>31</v>
       </c>
       <c r="F178" s="4">
-        <v>6</v>
+        <v>5.08</v>
       </c>
       <c r="G178" s="2">
         <v>130</v>
@@ -6190,7 +6245,7 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B179">
         <v>16</v>
@@ -6205,7 +6260,7 @@
         <v>36</v>
       </c>
       <c r="F179" s="4">
-        <v>7</v>
+        <v>4.76</v>
       </c>
       <c r="G179" s="2">
         <v>130</v>
@@ -6219,7 +6274,7 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B180">
         <v>16</v>
@@ -6234,7 +6289,7 @@
         <v>41</v>
       </c>
       <c r="F180" s="4">
-        <v>8</v>
+        <v>13.16</v>
       </c>
       <c r="G180" s="2">
         <v>130</v>
@@ -6248,7 +6303,7 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B181">
         <v>17</v>
@@ -6263,7 +6318,7 @@
         <v>0</v>
       </c>
       <c r="F181" s="4">
-        <v>1</v>
+        <v>2.96</v>
       </c>
       <c r="G181" s="2">
         <v>99</v>
@@ -6277,7 +6332,7 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B182">
         <v>17</v>
@@ -6292,7 +6347,7 @@
         <v>5</v>
       </c>
       <c r="F182" s="4">
-        <v>2</v>
+        <v>3.38</v>
       </c>
       <c r="G182" s="2">
         <v>99</v>
@@ -6306,7 +6361,7 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B183">
         <v>17</v>
@@ -6321,7 +6376,7 @@
         <v>10</v>
       </c>
       <c r="F183" s="4">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="G183" s="2">
         <v>99</v>
@@ -6335,7 +6390,7 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B184">
         <v>17</v>
@@ -6350,7 +6405,7 @@
         <v>15</v>
       </c>
       <c r="F184" s="4">
-        <v>4</v>
+        <v>3.12</v>
       </c>
       <c r="G184" s="2">
         <v>99</v>
@@ -6364,7 +6419,7 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B185">
         <v>17</v>
@@ -6379,7 +6434,7 @@
         <v>20</v>
       </c>
       <c r="F185" s="4">
-        <v>5</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="G185" s="2">
         <v>99</v>
@@ -6393,7 +6448,7 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B186">
         <v>17</v>
@@ -6408,7 +6463,7 @@
         <v>25</v>
       </c>
       <c r="F186" s="4">
-        <v>6</v>
+        <v>2.74</v>
       </c>
       <c r="G186" s="2">
         <v>99</v>
@@ -6422,7 +6477,7 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B187">
         <v>17</v>
@@ -6437,7 +6492,7 @@
         <v>30</v>
       </c>
       <c r="F187" s="4">
-        <v>7</v>
+        <v>2.74</v>
       </c>
       <c r="G187" s="2">
         <v>99</v>
@@ -6451,7 +6506,7 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B188">
         <v>17</v>
@@ -6466,7 +6521,7 @@
         <v>35</v>
       </c>
       <c r="F188" s="4">
-        <v>8</v>
+        <v>3.54</v>
       </c>
       <c r="G188" s="2">
         <v>99</v>
@@ -6480,7 +6535,7 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B189">
         <v>18</v>
@@ -6495,7 +6550,7 @@
         <v>0</v>
       </c>
       <c r="F189" s="4">
-        <v>1</v>
+        <v>2.91</v>
       </c>
       <c r="G189" s="2">
         <v>132</v>
@@ -6509,7 +6564,7 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B190">
         <v>18</v>
@@ -6524,7 +6579,7 @@
         <v>5</v>
       </c>
       <c r="F190" s="4">
-        <v>2</v>
+        <v>4.7699999999999996</v>
       </c>
       <c r="G190" s="2">
         <v>179</v>
@@ -6538,7 +6593,7 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B191">
         <v>18</v>
@@ -6553,7 +6608,7 @@
         <v>10</v>
       </c>
       <c r="F191" s="4">
-        <v>3</v>
+        <v>6.05</v>
       </c>
       <c r="G191" s="2">
         <v>214</v>
@@ -6567,7 +6622,7 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B192">
         <v>18</v>
@@ -6582,7 +6637,7 @@
         <v>15</v>
       </c>
       <c r="F192" s="4">
-        <v>4</v>
+        <v>3.36</v>
       </c>
       <c r="G192" s="2">
         <v>200</v>
@@ -6596,7 +6651,7 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B193">
         <v>18</v>
@@ -6611,7 +6666,7 @@
         <v>20</v>
       </c>
       <c r="F193" s="4">
-        <v>5</v>
+        <v>3.11</v>
       </c>
       <c r="G193" s="2">
         <v>199</v>
@@ -6625,7 +6680,7 @@
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B194">
         <v>18</v>
@@ -6640,7 +6695,7 @@
         <v>25</v>
       </c>
       <c r="F194" s="4">
-        <v>6</v>
+        <v>2.97</v>
       </c>
       <c r="G194" s="2">
         <v>200</v>
@@ -6654,7 +6709,7 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B195">
         <v>18</v>
@@ -6669,7 +6724,7 @@
         <v>30</v>
       </c>
       <c r="F195" s="4">
-        <v>7</v>
+        <v>3.34</v>
       </c>
       <c r="G195" s="2">
         <v>200</v>
@@ -6683,7 +6738,7 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B196">
         <v>18</v>
@@ -6698,7 +6753,7 @@
         <v>35</v>
       </c>
       <c r="F196" s="4">
-        <v>8</v>
+        <v>5.55</v>
       </c>
       <c r="G196" s="2">
         <v>200</v>
@@ -6712,7 +6767,7 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B197">
         <v>18</v>
@@ -6727,7 +6782,7 @@
         <v>40</v>
       </c>
       <c r="F197" s="4">
-        <v>9</v>
+        <v>7.09</v>
       </c>
       <c r="G197" s="2">
         <v>200</v>
@@ -6741,7 +6796,7 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B198">
         <v>18</v>
@@ -6756,7 +6811,7 @@
         <v>42</v>
       </c>
       <c r="F198" s="4">
-        <v>10</v>
+        <v>4.22</v>
       </c>
       <c r="G198" s="2">
         <v>162</v>
@@ -6770,7 +6825,7 @@
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B199">
         <v>18</v>
@@ -6785,7 +6840,7 @@
         <v>47</v>
       </c>
       <c r="F199" s="4">
-        <v>11</v>
+        <v>2.23</v>
       </c>
       <c r="G199" s="2">
         <v>167</v>
@@ -6798,7 +6853,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1" xr:uid="{9D72FA4F-E2D9-42B9-809F-A6413EE8998C}"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" priority="1"/>
     <cfRule type="colorScale" priority="2">
@@ -6813,13 +6867,19 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1BBE8D6-39CA-7F44-81E8-2B0BB2DB2329}">
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="35.5" customWidth="1"/>
+    <col min="2" max="2" width="29.5" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
@@ -6838,66 +6898,320 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="10">
+        <f>MIN(data!D:D)</f>
+        <v>1949</v>
+      </c>
+      <c r="E2" s="10">
+        <f>MAX(data!D:D)</f>
+        <v>1994</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>1</v>
+        <v>6</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D3" s="10">
+        <f>MIN(data!E:E)</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="10">
+        <f>MAX(data!E:E)</f>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
-        <v>2</v>
+        <v>7</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="10">
+        <f>MIN(data!F:F)</f>
+        <v>1.23</v>
+      </c>
+      <c r="E4" s="10">
+        <f>MAX(data!F:F)</f>
+        <v>18.010000000000002</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="8" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="8" t="s">
-        <v>27</v>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10">
+        <f>MAX(data!G:G)</f>
+        <v>513</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1" xr:uid="{D1BBE8D6-39CA-7F44-81E8-2B0BB2DB2329}"/>
-  <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" priority="1"/>
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000746DBEF59C7C747B0F132B24B64F945" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c08445d72d49c543b7c6b2163d0f313a">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="74573a3b-67d0-482f-8cf7-a6309fc98b14" xmlns:ns4="838992f0-d416-49bc-b59a-d86899b2f1c6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4a82c45bdd3579c3526b965f57664831" ns3:_="" ns4:_="">
+    <xsd:import namespace="74573a3b-67d0-482f-8cf7-a6309fc98b14"/>
+    <xsd:import namespace="838992f0-d416-49bc-b59a-d86899b2f1c6"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:_activity" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns4:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns4:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns4:SharingHintHash" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="74573a3b-67d0-482f-8cf7-a6309fc98b14" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_activity" ma:index="10" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="15" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="16" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="838992f0-d416-49bc-b59a-d86899b2f1c6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="12" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="13" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="SharingHintHash" ma:index="14" nillable="true" ma:displayName="Sharing Hint Hash" ma:hidden="true" ma:internalName="SharingHintHash" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="74573a3b-67d0-482f-8cf7-a6309fc98b14" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA245298-FC3C-4293-B359-D546A0712E7D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="74573a3b-67d0-482f-8cf7-a6309fc98b14"/>
+    <ds:schemaRef ds:uri="838992f0-d416-49bc-b59a-d86899b2f1c6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6B799F4-3DD0-40A0-8525-AED65C6A0E42}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="74573a3b-67d0-482f-8cf7-a6309fc98b14"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6AF8D2C7-A787-46EC-A486-160E19784237}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>